--- a/TESTS/zlit_5_pollianna.xlsx
+++ b/TESTS/zlit_5_pollianna.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Елеанор Портер — американська письменниця</t>
+          <t>Елеанор Портер</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>США — Портер народилась у Нью-Гемпширі у 1868 році</t>
+          <t>США</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>США — маленьке американське містечко де живе сувора тітка Поллі</t>
+          <t>США</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Полліанна — дівчинка-сирота яку після смерті батька відправляють до суворої тітки Поллі</t>
+          <t>Полліанна</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Незвично радісним і оптимістичним — вона завжди знаходить привід для радості навіть у найгіршій ситуації</t>
+          <t>Незвично радісним і оптимістичним</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Батько навчив її «грі в радість» — у будь-якій ситуації знаходити те чому можна бути вдячним</t>
+          <t>Батько навчив її «грі в радість»</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Пошук у будь-якій ситуації хоча б чогось радісного — навіть у поганому знайти щось хороше</t>
+          <t>Пошук у будь-якій ситуації хоча б чогось радісного</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Батько навчив її коли вони чекали ляльку в гуманітарній допомозі та отримали милиці — радісним було те що ти не потребуєш милиць</t>
+          <t>Батько навчив її коли вони чекали ляльку в гуманітарній допомозі та отримали милиці</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Жити у темній горищній кімнаті — але вона знаходить радість у чудовому краєвиді з вікна</t>
+          <t>Жити у темній горищній кімнаті</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чому Полліанна переїхала жити до тітки Поллі?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Батьки відправили її на навчання</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Її батько-священник помер, і вона залишилась сиротою без рідних, крім тітки</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона сама захотіла переїхати</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Тітка взяла її в гості на літо</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Яке враження справила на тітку Поллі звістка про приїзд племінниці?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона зраділа</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона прийняла Полліанну з почуття обов'язку, без особливої радості</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона відмовилась прийняти її</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона нічого не знала про неї</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>У яку кімнату тітка Поллі спершу оселила Полліанну?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У найкращу кімнату будинку</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У просту горищну кімнату без прикрас, хоч у будинку були й кращі</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У кімнату для гостей</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У кімнату служниці</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Як Полліанна відреагувала, побачивши свою просту горищну кімнату без дзеркала і картин?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Розплакалась і пожалілась</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зраділа чудовому виду з вікна і тому, що не треба дивитися в дзеркало на ластовиння</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розгнівалась на тітку</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сказала, що поскаржиться</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Як служниця Нансі поставилась до незвичної звички Полліанни знаходити радість у всьому?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Одразу зрозуміла й підтримала</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спершу дивувалась, але поступово й сама захопилась цією грою</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розсердилась на дівчинку</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не звернула уваги</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Чого, на думку Полліанни, не варто було б давати дітям, навіть якщо вони цього не люблять?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Іграшок</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Нічого — у грі в радість важливо знайти добре навіть у тому, що спершу здається поганим</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Книжок</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Друзів</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Кого Полліанна випадково зустріла на вулиці і одразу почала з ним приязно розмовляти?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лікаря</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Угрюмого пана Джона Пендлтона, якого всі вважали відлюдьком</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Священника</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Поліцейського</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Як спочатку відреагував пан Пендлтон на привітну й балакучу Полліанну?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зрадів спілкуванню</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Грубо й роздратовано, бажаючи, щоб його залишили на самоті</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Запросив її в гості</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не помітив її</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Кого ще Полліанна відвідувала й підтримувала своїми оптимістичними розмовами?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише тітку</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Хвору, прикуту до ліжка місіс Сноу, яка постійно скаржилась на життя</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише дітей сусідів</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише вчителів школи</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Якою була місіс Сноу до того, як Полліанна почала її відвідувати?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Веселою і доброю до всіх</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Постійно невдоволеною, дратівливою і нещасною через свою хворобу</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дуже релігійною</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Самотньою без родини</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Як Полліанна змінила ставлення місіс Сноу до власної хвороби?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не змінила</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Навчила її «грі в радість» — знаходити щось хороше навіть у поганих днях</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Покликала лікаря</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Принесла їй ліки</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що зрештою сталося з настроєм і здоров'ям місіс Сноу завдяки спілкуванню з Полліанною?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не змінилось</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона стала набагато спокійнішою, добрішою і навіть почала цікавитись життям навколо</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона захворіла ще більше</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона переїхала геть</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що Полліанна дізналася про пана Пендлтона, проводячи з ним більше часу?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Що він злий назавжди</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Що під суворістю він приховує самотність і колишню нерозділену любов до її матері</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що він багатий злодій</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що він батько Полліанни</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що пан Пендлтон запропонував Полліанні, коли побачив, як вона змінює людей навколо?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Гроші</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Залишитись жити в нього, бо в його великому будинку самотньо</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Подарунок і нічого більше</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він нічого не запропонував</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як Полліанна відповіла на пропозицію пана Пендлтона переїхати до нього?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Одразу погодилась і покинула тітку</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Подякувала, але лишилась із тіткою Поллі, бо та її потребувала</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розсердилась</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не зрозуміла питання</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що сталося з Полліанною, коли вона переходила вулицю?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого, вона завжди обережна</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Її збив автомобіль, і вона отримала серйозну травму ніг</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона посковзнулась і забилась легко</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона захворіла на простуду</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Що лікарі сказали про ноги Полліанни після обстеження?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Що все швидко загоїться</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Що вона, можливо, ніколи більше не зможе ходити</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що потрібна лише пара днів відпочинку</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого конкретного не сказали</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як уперше за весь час Полліанна не змогла застосувати «гру в радість»?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона легко знайшла радість і в цьому</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона довго не могла вигадати, чому варто радіти, що втратила здатність ходити</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона взагалі не журилась</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона одразу здалася назавжди</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Як на новину про травму Полліанни відреагували мешканці міста, яким вона раніше допомагала?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нікому було байдуже</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Багато хто, кого вона навчила «грі в радість», прийшли підтримати й віддячити їй тим самим</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Усі забули про неї</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише тітка прийшла</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Що зрештою допомогло Полліанні знову повірити, що вона зможе одужати?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ліки лікаря</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Підтримка людей, яким вона колись подарувала радість, і власна гра в радість, застосована до себе</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Гроші пана Пендлтона</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Переїзд в інше місто</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Як змінилась тітка Поллі за час, що Полліанна жила з нею?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не змінилась зовсім</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Стала теплішою, навчилась радіти і відкрито любити племінницю</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Стала ще суворішою</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Виїхала з міста</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що означає слово «полліанна» у сучасному вжитку?</t>
+          <t>Слово «полліанна» в сучасній англійській мові вживають для опису надмірно оптимістичної людини.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яку психологічну ідею несе «гра в радість»?</t>
+          <t>«Гра в радість» вчить шукати щось хороше навіть у складних ситуаціях, не заперечуючи самі труднощі.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яка традиція американської дитячої літератури відображена у «Полліанні»?</t>
+          <t>Книги про дівчаток-сиріток, що своєю добротою змінюють оточення, — поширена традиція американської дитячої літератури.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яке лихо спіткало Полліанну і як вона з ним справлялась?</t>
+          <t>Полліанну збив автомобіль, і лікарі побоювались, що вона не зможе ходити.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Що допомогло Полліанні одужати після трагедії?</t>
+          <t>Одужанню Полліанни допомогла підтримка людей, яких вона раніше навчила радості.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея книги «Полліанна»?</t>
+          <t>Головна ідея книги — оптимізм і доброта однієї людини можуть змінити цілу громаду.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2141,17 +2323,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Стару місіс Сноу — похмуру хвору жінку</t>
+          <t>Стару місіс Сноу</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Суворого пана Пендлтона — самотнього відлюдника</t>
+          <t>Суворого пана Пендлтона</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Всіх жителів міста — місто стало радіснішим</t>
+          <t>Всіх жителів міста</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2167,6 +2349,11 @@
       <c r="H41" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,37 +2412,42 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Яких людей змінила Полліанна своїм оптимізмом?</t>
+          <t>Що сталося з Полліанною після нещасного випадку на дорозі?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Стару місіс Сноу — похмуру хвору жінку</t>
+          <t>Лікарі побоювались, що вона не ходитиме</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Суворого пана Пендлтона — самотнього відлюдника</t>
+          <t>Місто згадало про її доброту і підтримало її</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Всіх жителів міста — місто стало радіснішим</t>
+          <t>Вона одразу одужала</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Тітку Поллі — сувору господиню</t>
+          <t>Спершу їй було важко застосувати «гру в радість» до себе</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>А,Б,В</t>
+          <t>А,Б,Г</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Своїм оптимізмом і добротою вона поступово змінює похмурих нещасних людей — вони починають радіти</t>
+          <t>Своїм оптимізмом і добротою вона поступово змінює похмурих нещасних людей</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Серце тітки поступово розм'якшується — вона починає любити Полліанну і сама вчиться радіти</t>
+          <t>Серце тітки поступово розм'якшується</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
